--- a/docs/s2t_task/s2t_files_examples/json_S2T_пример JSON.xlsx
+++ b/docs/s2t_task/s2t_files_examples/json_S2T_пример JSON.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KDanilchenko\Documents\_Data Lineage_\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/synikolaev/data_lineage_monorepo/docs/s2t_task/s2t_files_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA0523AB-4A6D-4B2B-87E8-05E141A2471E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FEA9C0-D6FB-494F-A765-3FE33E41EDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="0" windowWidth="37230" windowHeight="12810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Порядковый номер строки маппинга</t>
         </r>
@@ -47,6 +48,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Номер версии документа, соответствующий последним изменениям алгоритма.</t>
         </r>
@@ -60,6 +62,7 @@
             <sz val="8"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Указываем наименование БД в случае с Oracle, PostgreSQL, MS SLQ и другими системами, где предусмотрено наличие БД. Для других систем указываем их название, например DRP, КХД, Стримминговая платформа и т.д.</t>
         </r>
@@ -67,6 +70,7 @@
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -81,6 +85,7 @@
             <sz val="8"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Схема таблицы-источника</t>
         </r>
@@ -88,6 +93,7 @@
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -102,6 +108,7 @@
             <sz val="8"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Таблица источника</t>
         </r>
@@ -109,6 +116,7 @@
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -122,6 +130,7 @@
             <sz val="8"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Код атрибута</t>
         </r>
@@ -129,6 +138,7 @@
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -142,6 +152,7 @@
             <sz val="8"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Краткое наименование атрибута таблицы-источника</t>
         </r>
@@ -149,6 +160,7 @@
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -163,6 +175,7 @@
             <sz val="8"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Тип данных атрибута</t>
         </r>
@@ -170,6 +183,7 @@
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -184,6 +198,7 @@
             <sz val="8"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Длина/разрядность/точность атрибута</t>
         </r>
@@ -191,6 +206,7 @@
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -204,6 +220,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Перечисление наборов данных, используемых для заполнения целевых таблиц.</t>
         </r>
@@ -216,6 +233,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Перечисление алгоритмов, которые используются для заполнения атрибута таблицы-приемника</t>
         </r>
@@ -228,6 +246,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Комментарий к алгоритму</t>
         </r>
@@ -240,6 +259,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Статус по алгоритму</t>
         </r>
@@ -252,6 +272,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Номер версии документа, соответствующий последним изменениям алгоритма.</t>
         </r>
@@ -265,6 +286,7 @@
             <sz val="8"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Указываем наименование БД в случае с Oracle, PostgreSQL, MS SLQ и другими системами, где предусмотрено наличие БД. Для других систем указываем их название, например DRP, КХД, Стримминговая платформа и т.д.</t>
         </r>
@@ -272,6 +294,7 @@
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -285,6 +308,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Целевая схема данных таблицы-приемника</t>
         </r>
@@ -297,6 +321,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Наименование таблицы-приемника</t>
         </r>
@@ -309,6 +334,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Код атрибута таблицы-приемника</t>
         </r>
@@ -321,6 +347,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Краткое наименование атрибута таблицы-приемника</t>
         </r>
@@ -333,6 +360,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Расширенное описание атрибута таблицы-приемника</t>
         </r>
@@ -345,6 +373,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Тип данных атрибута</t>
         </r>
@@ -357,6 +386,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Длина/разрядность/точность атрибута</t>
         </r>
@@ -369,6 +399,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Признак вхождения атрибута в первичный ключ (в формате ‘x’)</t>
         </r>
@@ -381,6 +412,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Признак вхождения атрибута во внешний ключ (в формате ‘x’)</t>
         </r>
@@ -393,6 +425,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Признак атрибута, который не может принимать значения NULL (в формате ‘x’)</t>
         </r>
@@ -405,6 +438,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Признак атрибута (в формате ‘x’), по которому нужно отслеживать реджекты. </t>
         </r>
@@ -417,6 +451,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Признак атрибута (в формате ‘x’), для которого нужно отслеживать появление новых справочных значений на источнике и автоматически заносить их в перекодировочную таблицу. Применяется только для атрибутов, ссылающихся на справочник CL.</t>
         </r>
@@ -427,7 +462,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="495">
   <si>
     <t>Source/Target</t>
   </si>
@@ -440,6 +475,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -456,6 +492,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -472,6 +509,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -485,6 +523,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -498,6 +537,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -511,6 +551,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -524,6 +565,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -540,6 +582,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -553,6 +596,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -569,6 +613,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -591,6 +636,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -604,6 +650,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -617,6 +664,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -630,6 +678,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -643,6 +692,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -656,6 +706,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -678,6 +729,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -703,6 +755,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -731,6 +784,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -765,6 +819,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -774,6 +829,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -790,6 +846,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -803,6 +860,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -815,6 +873,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -828,6 +887,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -841,6 +901,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -853,6 +914,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -866,6 +928,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -879,6 +942,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -891,6 +955,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -901,6 +966,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -917,6 +983,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -930,6 +997,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -942,6 +1010,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -952,6 +1021,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -968,6 +1038,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -981,6 +1052,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -993,6 +1065,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1006,6 +1079,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1019,6 +1093,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1031,6 +1106,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1044,6 +1120,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1057,6 +1134,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1069,6 +1147,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1082,6 +1161,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1095,6 +1175,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1104,6 +1185,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1120,6 +1202,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1132,6 +1215,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1148,6 +1232,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1164,6 +1249,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1180,6 +1266,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1205,6 +1292,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1221,6 +1309,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1237,6 +1326,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1253,6 +1343,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1272,6 +1363,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1294,6 +1386,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1310,6 +1403,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1341,6 +1435,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1363,6 +1458,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1379,6 +1475,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1392,6 +1489,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1420,6 +1518,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1436,6 +1535,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1458,6 +1558,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1480,6 +1581,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1505,6 +1607,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1521,6 +1624,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1630,6 +1734,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1718,6 +1823,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1773,6 +1879,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1786,6 +1893,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -1802,6 +1910,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>JSON_MODEL3882-V1</t>
     </r>
@@ -2408,13 +2517,25 @@
   </si>
   <si>
     <t>loanApplication.legalEntity.individuals.snils</t>
+  </si>
+  <si>
+    <t>JSON_MODEL69666</t>
+  </si>
+  <si>
+    <t>loanApplication.creditParameters.leasingDevilCars</t>
+  </si>
+  <si>
+    <t>loanApplication.creditParameters.leasingDevilCars2</t>
+  </si>
+  <si>
+    <t>JSON_MODEL69666-V2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2423,44 +2544,63 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2860,130 +3000,133 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+  <cellXfs count="43">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -3206,84 +3349,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF391"/>
-  <sheetFormatPr defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF393"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="44" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="68.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="77.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="36.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="81.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="23" style="1" customWidth="1"/>
+    <col min="22" max="22" width="68.5" style="1" customWidth="1"/>
+    <col min="23" max="23" width="77.33203125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="36.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="81.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="29" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="33.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="33.140625" style="1"/>
+    <col min="31" max="31" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="33.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="33.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="10" t="s">
+      <c r="D1" s="26"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="11"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="23"/>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="T1" s="12"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="24"/>
+    </row>
+    <row r="2" spans="1:32" ht="14" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -3381,12 +3524,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E3" s="4"/>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="4" t="s">
         <v>67</v>
       </c>
       <c r="V3" s="4" t="s">
@@ -3397,12 +3540,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E4" s="4"/>
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4"/>
-      <c r="U4" s="9" t="s">
+      <c r="U4" s="4" t="s">
         <v>74</v>
       </c>
       <c r="V4" s="4" t="s">
@@ -3413,12 +3556,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E5" s="4"/>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5"/>
-      <c r="U5" s="9" t="s">
+      <c r="U5" s="4" t="s">
         <v>80</v>
       </c>
       <c r="V5" s="4" t="s">
@@ -3429,12 +3572,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E6" s="4"/>
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6"/>
-      <c r="U6" s="9" t="s">
+      <c r="U6" s="4" t="s">
         <v>86</v>
       </c>
       <c r="V6" s="4" t="s">
@@ -3445,12 +3588,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="18.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="18.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E7" s="4"/>
       <c r="G7"/>
       <c r="H7"/>
       <c r="I7"/>
-      <c r="U7" s="9" t="s">
+      <c r="U7" s="4" t="s">
         <v>94</v>
       </c>
       <c r="V7" s="4" t="s">
@@ -3461,12 +3604,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E8" s="4"/>
       <c r="G8"/>
       <c r="H8"/>
       <c r="I8"/>
-      <c r="U8" s="9" t="s">
+      <c r="U8" s="4" t="s">
         <v>102</v>
       </c>
       <c r="V8" s="4" t="s">
@@ -3477,12 +3620,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E9" s="4"/>
       <c r="G9"/>
       <c r="H9"/>
       <c r="I9"/>
-      <c r="U9" s="9" t="s">
+      <c r="U9" s="4" t="s">
         <v>108</v>
       </c>
       <c r="V9" s="4" t="s">
@@ -3493,12 +3636,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E10" s="4"/>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10"/>
-      <c r="U10" s="9" t="s">
+      <c r="U10" s="4" t="s">
         <v>114</v>
       </c>
       <c r="V10" s="4" t="s">
@@ -3509,12 +3652,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E11" s="4"/>
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11"/>
-      <c r="U11" s="9" t="s">
+      <c r="U11" s="4" t="s">
         <v>119</v>
       </c>
       <c r="V11" s="4" t="s">
@@ -3525,12 +3668,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="E12" s="4"/>
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12"/>
-      <c r="U12" s="9" t="s">
+      <c r="U12" s="4" t="s">
         <v>124</v>
       </c>
       <c r="V12" s="4" t="s">
@@ -3541,7 +3684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" ht="16" x14ac:dyDescent="0.2">
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
@@ -3555,7 +3698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" ht="16" x14ac:dyDescent="0.2">
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14"/>
@@ -3569,7 +3712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" ht="16" x14ac:dyDescent="0.2">
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15"/>
@@ -3583,7 +3726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="16" x14ac:dyDescent="0.2">
       <c r="G16"/>
       <c r="H16"/>
       <c r="I16"/>
@@ -3597,7 +3740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
@@ -3611,7 +3754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18"/>
@@ -3625,7 +3768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G19"/>
       <c r="H19"/>
       <c r="I19"/>
@@ -3639,7 +3782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G20"/>
       <c r="H20"/>
       <c r="I20"/>
@@ -3653,7 +3796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
@@ -3667,7 +3810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
@@ -3681,7 +3824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
@@ -3695,7 +3838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
@@ -3709,7 +3852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
@@ -3723,7 +3866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
@@ -3737,7 +3880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
@@ -3751,7 +3894,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
@@ -3765,7 +3908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
@@ -3779,7 +3922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
@@ -3793,7 +3936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31"/>
@@ -3807,7 +3950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
@@ -3821,7 +3964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G33"/>
       <c r="H33"/>
       <c r="I33"/>
@@ -3835,7 +3978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G34"/>
       <c r="H34"/>
       <c r="I34"/>
@@ -3849,7 +3992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G35"/>
       <c r="H35"/>
       <c r="I35"/>
@@ -3863,7 +4006,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G36"/>
       <c r="H36"/>
       <c r="I36"/>
@@ -3877,7 +4020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G37"/>
       <c r="H37"/>
       <c r="I37"/>
@@ -3891,7 +4034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G38"/>
       <c r="H38"/>
       <c r="I38"/>
@@ -3905,7 +4048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G39"/>
       <c r="H39"/>
       <c r="I39"/>
@@ -3919,7 +4062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G40"/>
       <c r="H40"/>
       <c r="I40"/>
@@ -3933,7 +4076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41"/>
@@ -3947,7 +4090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42"/>
@@ -3961,7 +4104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43"/>
@@ -3975,7 +4118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G44"/>
       <c r="H44"/>
       <c r="I44"/>
@@ -3989,7 +4132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G45"/>
       <c r="H45"/>
       <c r="I45"/>
@@ -4003,7 +4146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G46"/>
       <c r="H46"/>
       <c r="I46"/>
@@ -4017,7 +4160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G47"/>
       <c r="H47"/>
       <c r="I47"/>
@@ -4031,7 +4174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G48"/>
       <c r="H48"/>
       <c r="I48"/>
@@ -4045,7 +4188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G49"/>
       <c r="H49"/>
       <c r="I49"/>
@@ -4059,7 +4202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G50"/>
       <c r="H50"/>
       <c r="I50"/>
@@ -4073,7 +4216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G51"/>
       <c r="H51"/>
       <c r="I51"/>
@@ -4087,7 +4230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G52"/>
       <c r="H52"/>
       <c r="I52"/>
@@ -4101,7 +4244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G53"/>
       <c r="H53"/>
       <c r="I53"/>
@@ -4115,7 +4258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G54"/>
       <c r="H54"/>
       <c r="I54"/>
@@ -4129,7 +4272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G55"/>
       <c r="H55"/>
       <c r="I55"/>
@@ -4143,7 +4286,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G56"/>
       <c r="H56"/>
       <c r="I56"/>
@@ -4157,7 +4300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G57"/>
       <c r="H57"/>
       <c r="I57"/>
@@ -4171,7 +4314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G58"/>
       <c r="H58"/>
       <c r="I58"/>
@@ -4185,7 +4328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G59"/>
       <c r="H59"/>
       <c r="I59"/>
@@ -4199,7 +4342,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G60"/>
       <c r="H60"/>
       <c r="I60"/>
@@ -4213,7 +4356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G61"/>
       <c r="H61"/>
       <c r="I61"/>
@@ -4227,7 +4370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G62"/>
       <c r="H62"/>
       <c r="I62"/>
@@ -4241,7 +4384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G63"/>
       <c r="H63"/>
       <c r="I63"/>
@@ -4255,7 +4398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G64"/>
       <c r="H64"/>
       <c r="I64"/>
@@ -4269,7 +4412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G65"/>
       <c r="H65"/>
       <c r="I65"/>
@@ -4283,7 +4426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G66"/>
       <c r="H66"/>
       <c r="I66"/>
@@ -4297,7 +4440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G67"/>
       <c r="H67"/>
       <c r="I67"/>
@@ -4311,7 +4454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G68"/>
       <c r="H68"/>
       <c r="I68"/>
@@ -4325,7 +4468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G69"/>
       <c r="H69"/>
       <c r="I69"/>
@@ -4339,7 +4482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G70"/>
       <c r="H70"/>
       <c r="I70"/>
@@ -4353,7 +4496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G71"/>
       <c r="H71"/>
       <c r="I71"/>
@@ -4367,7 +4510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G72"/>
       <c r="H72"/>
       <c r="I72"/>
@@ -4381,7 +4524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G73"/>
       <c r="H73"/>
       <c r="I73"/>
@@ -4395,7 +4538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G74"/>
       <c r="H74"/>
       <c r="I74"/>
@@ -4409,7 +4552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G75"/>
       <c r="H75"/>
       <c r="I75"/>
@@ -4423,7 +4566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G76"/>
       <c r="H76"/>
       <c r="I76"/>
@@ -4437,7 +4580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
@@ -4451,7 +4594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G78"/>
       <c r="H78"/>
       <c r="I78"/>
@@ -4465,7 +4608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G79"/>
       <c r="H79"/>
       <c r="I79"/>
@@ -4479,7 +4622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G80"/>
       <c r="H80"/>
       <c r="I80"/>
@@ -4493,7 +4636,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G81"/>
       <c r="H81"/>
       <c r="I81"/>
@@ -4507,7 +4650,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G82"/>
       <c r="H82"/>
       <c r="I82"/>
@@ -4521,7 +4664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G83"/>
       <c r="H83"/>
       <c r="I83"/>
@@ -4535,7 +4678,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G84"/>
       <c r="H84"/>
       <c r="I84"/>
@@ -4549,7 +4692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G85"/>
       <c r="H85"/>
       <c r="I85"/>
@@ -4563,7 +4706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G86"/>
       <c r="H86"/>
       <c r="I86"/>
@@ -4577,7 +4720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G87"/>
       <c r="H87"/>
       <c r="I87"/>
@@ -4591,7 +4734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G88"/>
       <c r="H88"/>
       <c r="I88"/>
@@ -4605,7 +4748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G89"/>
       <c r="H89"/>
       <c r="I89"/>
@@ -4619,7 +4762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G90"/>
       <c r="H90"/>
       <c r="I90"/>
@@ -4633,7 +4776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G91"/>
       <c r="H91"/>
       <c r="I91"/>
@@ -4647,7 +4790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G92"/>
       <c r="H92"/>
       <c r="I92"/>
@@ -4661,7 +4804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G93"/>
       <c r="H93"/>
       <c r="I93"/>
@@ -4675,7 +4818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G94"/>
       <c r="H94"/>
       <c r="I94"/>
@@ -4689,7 +4832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G95"/>
       <c r="H95"/>
       <c r="I95"/>
@@ -4703,7 +4846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G96"/>
       <c r="H96"/>
       <c r="I96"/>
@@ -4717,7 +4860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G97"/>
       <c r="H97"/>
       <c r="I97"/>
@@ -4731,7 +4874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G98"/>
       <c r="H98"/>
       <c r="I98"/>
@@ -4745,7 +4888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G99"/>
       <c r="H99"/>
       <c r="I99"/>
@@ -4759,7 +4902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G100"/>
       <c r="H100"/>
       <c r="I100"/>
@@ -4773,7 +4916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G101"/>
       <c r="H101"/>
       <c r="I101"/>
@@ -4787,7 +4930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G102"/>
       <c r="H102"/>
       <c r="I102"/>
@@ -4801,7 +4944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G103"/>
       <c r="H103"/>
       <c r="I103"/>
@@ -4815,7 +4958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G104"/>
       <c r="H104"/>
       <c r="I104"/>
@@ -4829,7 +4972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G105"/>
       <c r="H105"/>
       <c r="I105"/>
@@ -4843,7 +4986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G106"/>
       <c r="H106"/>
       <c r="I106"/>
@@ -4857,7 +5000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G107"/>
       <c r="H107"/>
       <c r="I107"/>
@@ -4871,7 +5014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G108"/>
       <c r="H108"/>
       <c r="I108"/>
@@ -4885,7 +5028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G109"/>
       <c r="H109"/>
       <c r="I109"/>
@@ -4899,7 +5042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G110"/>
       <c r="H110"/>
       <c r="I110"/>
@@ -4913,7 +5056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G111"/>
       <c r="H111"/>
       <c r="I111"/>
@@ -4927,7 +5070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G112"/>
       <c r="H112"/>
       <c r="I112"/>
@@ -4941,7 +5084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G113"/>
       <c r="H113"/>
       <c r="I113"/>
@@ -4955,7 +5098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G114"/>
       <c r="H114"/>
       <c r="I114"/>
@@ -4969,7 +5112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G115"/>
       <c r="H115"/>
       <c r="I115"/>
@@ -4983,7 +5126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G116"/>
       <c r="H116"/>
       <c r="I116"/>
@@ -4997,7 +5140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G117"/>
       <c r="H117"/>
       <c r="I117"/>
@@ -5011,7 +5154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G118"/>
       <c r="H118"/>
       <c r="I118"/>
@@ -5025,7 +5168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G119"/>
       <c r="H119"/>
       <c r="I119"/>
@@ -5039,7 +5182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G120"/>
       <c r="H120"/>
       <c r="I120"/>
@@ -5053,7 +5196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G121"/>
       <c r="H121"/>
       <c r="I121"/>
@@ -5067,7 +5210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G122"/>
       <c r="H122"/>
       <c r="I122"/>
@@ -5081,7 +5224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G123"/>
       <c r="H123"/>
       <c r="I123"/>
@@ -5095,7 +5238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G124"/>
       <c r="H124"/>
       <c r="I124"/>
@@ -5109,7 +5252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G125"/>
       <c r="H125"/>
       <c r="I125"/>
@@ -5123,7 +5266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G126"/>
       <c r="H126"/>
       <c r="I126"/>
@@ -5137,7 +5280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G127"/>
       <c r="H127"/>
       <c r="I127"/>
@@ -5151,7 +5294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G128"/>
       <c r="H128"/>
       <c r="I128"/>
@@ -5165,7 +5308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G129"/>
       <c r="H129"/>
       <c r="I129"/>
@@ -5179,7 +5322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G130"/>
       <c r="H130"/>
       <c r="I130"/>
@@ -5193,7 +5336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G131"/>
       <c r="H131"/>
       <c r="I131"/>
@@ -5207,7 +5350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G132"/>
       <c r="H132"/>
       <c r="I132"/>
@@ -5221,7 +5364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G133"/>
       <c r="H133"/>
       <c r="I133"/>
@@ -5235,7 +5378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G134"/>
       <c r="H134"/>
       <c r="I134"/>
@@ -5249,7 +5392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G135"/>
       <c r="H135"/>
       <c r="I135"/>
@@ -5263,7 +5406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G136"/>
       <c r="H136"/>
       <c r="I136"/>
@@ -5277,7 +5420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G137"/>
       <c r="H137"/>
       <c r="I137"/>
@@ -5291,7 +5434,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G138"/>
       <c r="H138"/>
       <c r="I138"/>
@@ -5305,7 +5448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G139"/>
       <c r="H139"/>
       <c r="I139"/>
@@ -5319,7 +5462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G140"/>
       <c r="H140"/>
       <c r="I140"/>
@@ -5333,7 +5476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G141"/>
       <c r="H141"/>
       <c r="I141"/>
@@ -5347,7 +5490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G142"/>
       <c r="H142"/>
       <c r="I142"/>
@@ -5361,7 +5504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G143"/>
       <c r="H143"/>
       <c r="I143"/>
@@ -5375,7 +5518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G144"/>
       <c r="H144"/>
       <c r="I144"/>
@@ -5389,7 +5532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G145"/>
       <c r="H145"/>
       <c r="I145"/>
@@ -5403,7 +5546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G146"/>
       <c r="H146"/>
       <c r="I146"/>
@@ -5417,7 +5560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G147"/>
       <c r="H147"/>
       <c r="I147"/>
@@ -5431,7 +5574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G148"/>
       <c r="H148"/>
       <c r="I148"/>
@@ -5445,7 +5588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G149"/>
       <c r="H149"/>
       <c r="I149"/>
@@ -5459,7 +5602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G150"/>
       <c r="H150"/>
       <c r="I150"/>
@@ -5473,7 +5616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G151"/>
       <c r="H151"/>
       <c r="I151"/>
@@ -5487,7 +5630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G152"/>
       <c r="H152"/>
       <c r="I152"/>
@@ -5501,7 +5644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G153"/>
       <c r="H153"/>
       <c r="I153"/>
@@ -5515,7 +5658,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G154"/>
       <c r="H154"/>
       <c r="I154"/>
@@ -5529,7 +5672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G155"/>
       <c r="H155"/>
       <c r="I155"/>
@@ -5543,7 +5686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G156"/>
       <c r="H156"/>
       <c r="I156"/>
@@ -5557,7 +5700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G157"/>
       <c r="H157"/>
       <c r="I157"/>
@@ -5571,7 +5714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G158"/>
       <c r="H158"/>
       <c r="I158"/>
@@ -5585,7 +5728,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="159" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G159"/>
       <c r="H159"/>
       <c r="I159"/>
@@ -5599,7 +5742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G160"/>
       <c r="H160"/>
       <c r="I160"/>
@@ -5613,7 +5756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G161"/>
       <c r="H161"/>
       <c r="I161"/>
@@ -5627,7 +5770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G162"/>
       <c r="H162"/>
       <c r="I162"/>
@@ -5641,7 +5784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G163"/>
       <c r="H163"/>
       <c r="I163"/>
@@ -5655,7 +5798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G164"/>
       <c r="H164"/>
       <c r="I164"/>
@@ -5669,7 +5812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G165"/>
       <c r="H165"/>
       <c r="I165"/>
@@ -5683,7 +5826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G166"/>
       <c r="H166"/>
       <c r="I166"/>
@@ -5697,7 +5840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G167"/>
       <c r="H167"/>
       <c r="I167"/>
@@ -5711,7 +5854,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G168"/>
       <c r="H168"/>
       <c r="I168"/>
@@ -5725,7 +5868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G169"/>
       <c r="H169"/>
       <c r="I169"/>
@@ -5739,7 +5882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G170"/>
       <c r="H170"/>
       <c r="I170"/>
@@ -5753,7 +5896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G171"/>
       <c r="H171"/>
       <c r="I171"/>
@@ -5767,7 +5910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G172"/>
       <c r="H172"/>
       <c r="I172"/>
@@ -5781,7 +5924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G173"/>
       <c r="H173"/>
       <c r="I173"/>
@@ -5795,7 +5938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G174"/>
       <c r="H174"/>
       <c r="I174"/>
@@ -5809,7 +5952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G175"/>
       <c r="H175"/>
       <c r="I175"/>
@@ -5823,7 +5966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G176"/>
       <c r="H176"/>
       <c r="I176"/>
@@ -5837,7 +5980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G177"/>
       <c r="H177"/>
       <c r="I177"/>
@@ -5851,7 +5994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G178"/>
       <c r="H178"/>
       <c r="I178"/>
@@ -5865,7 +6008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G179"/>
       <c r="H179"/>
       <c r="I179"/>
@@ -5879,7 +6022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G180"/>
       <c r="H180"/>
       <c r="I180"/>
@@ -5893,7 +6036,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G181"/>
       <c r="H181"/>
       <c r="I181"/>
@@ -5907,7 +6050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G182"/>
       <c r="H182"/>
       <c r="I182"/>
@@ -5921,7 +6064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G183"/>
       <c r="H183"/>
       <c r="I183"/>
@@ -5935,7 +6078,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G184"/>
       <c r="H184"/>
       <c r="I184"/>
@@ -5949,7 +6092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G185"/>
       <c r="H185"/>
       <c r="I185"/>
@@ -5963,7 +6106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="186" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G186"/>
       <c r="H186"/>
       <c r="I186"/>
@@ -5977,7 +6120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="187" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G187"/>
       <c r="H187"/>
       <c r="I187"/>
@@ -5991,7 +6134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G188"/>
       <c r="H188"/>
       <c r="I188"/>
@@ -6005,7 +6148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="189" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G189"/>
       <c r="H189"/>
       <c r="I189"/>
@@ -6019,7 +6162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="190" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G190"/>
       <c r="H190"/>
       <c r="I190"/>
@@ -6033,7 +6176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G191"/>
       <c r="H191"/>
       <c r="I191"/>
@@ -6047,7 +6190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G192"/>
       <c r="H192"/>
       <c r="I192"/>
@@ -6061,7 +6204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G193"/>
       <c r="H193"/>
       <c r="I193"/>
@@ -6075,7 +6218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G194"/>
       <c r="H194"/>
       <c r="I194"/>
@@ -6089,7 +6232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G195"/>
       <c r="H195"/>
       <c r="I195"/>
@@ -6103,7 +6246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G196"/>
       <c r="H196"/>
       <c r="I196"/>
@@ -6117,7 +6260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G197"/>
       <c r="H197"/>
       <c r="I197"/>
@@ -6131,7 +6274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G198"/>
       <c r="H198"/>
       <c r="I198"/>
@@ -6145,7 +6288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G199"/>
       <c r="H199"/>
       <c r="I199"/>
@@ -6159,7 +6302,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G200"/>
       <c r="H200"/>
       <c r="I200"/>
@@ -6173,7 +6316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G201"/>
       <c r="H201"/>
       <c r="I201"/>
@@ -6187,7 +6330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G202"/>
       <c r="H202"/>
       <c r="I202"/>
@@ -6201,7 +6344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G203"/>
       <c r="H203"/>
       <c r="I203"/>
@@ -6215,7 +6358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G204"/>
       <c r="H204"/>
       <c r="I204"/>
@@ -6229,7 +6372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G205"/>
       <c r="H205"/>
       <c r="I205"/>
@@ -6243,7 +6386,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G206"/>
       <c r="H206"/>
       <c r="I206"/>
@@ -6257,7 +6400,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G207"/>
       <c r="H207"/>
       <c r="I207"/>
@@ -6271,7 +6414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G208"/>
       <c r="H208"/>
       <c r="I208"/>
@@ -6285,7 +6428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G209"/>
       <c r="H209"/>
       <c r="I209"/>
@@ -6299,7 +6442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G210"/>
       <c r="H210"/>
       <c r="I210"/>
@@ -6313,7 +6456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G211"/>
       <c r="H211"/>
       <c r="I211"/>
@@ -6327,7 +6470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G212"/>
       <c r="H212"/>
       <c r="I212"/>
@@ -6341,7 +6484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G213"/>
       <c r="H213"/>
       <c r="I213"/>
@@ -6355,7 +6498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G214"/>
       <c r="H214"/>
       <c r="I214"/>
@@ -6369,7 +6512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G215"/>
       <c r="H215"/>
       <c r="I215"/>
@@ -6383,7 +6526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G216"/>
       <c r="H216"/>
       <c r="I216"/>
@@ -6397,7 +6540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G217"/>
       <c r="H217"/>
       <c r="I217"/>
@@ -6411,7 +6554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G218"/>
       <c r="H218"/>
       <c r="I218"/>
@@ -6425,7 +6568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G219"/>
       <c r="H219"/>
       <c r="I219"/>
@@ -6439,7 +6582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="220" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G220"/>
       <c r="H220"/>
       <c r="I220"/>
@@ -6453,7 +6596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G221"/>
       <c r="H221"/>
       <c r="I221"/>
@@ -6467,7 +6610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G222"/>
       <c r="H222"/>
       <c r="I222"/>
@@ -6481,7 +6624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G223"/>
       <c r="H223"/>
       <c r="I223"/>
@@ -6495,7 +6638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="224" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G224"/>
       <c r="H224"/>
       <c r="I224"/>
@@ -6509,7 +6652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G225"/>
       <c r="H225"/>
       <c r="I225"/>
@@ -6523,7 +6666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="226" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G226"/>
       <c r="H226"/>
       <c r="I226"/>
@@ -6537,7 +6680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G227"/>
       <c r="H227"/>
       <c r="I227"/>
@@ -6551,7 +6694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="228" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G228"/>
       <c r="H228"/>
       <c r="I228"/>
@@ -6565,7 +6708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G229"/>
       <c r="H229"/>
       <c r="I229"/>
@@ -6579,7 +6722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="230" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G230"/>
       <c r="H230"/>
       <c r="I230"/>
@@ -6593,7 +6736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G231"/>
       <c r="H231"/>
       <c r="I231"/>
@@ -6607,7 +6750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G232"/>
       <c r="H232"/>
       <c r="I232"/>
@@ -6621,7 +6764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G233"/>
       <c r="H233"/>
       <c r="I233"/>
@@ -6635,7 +6778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G234"/>
       <c r="H234"/>
       <c r="I234"/>
@@ -6649,7 +6792,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G235"/>
       <c r="H235"/>
       <c r="I235"/>
@@ -6663,7 +6806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="236" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G236"/>
       <c r="H236"/>
       <c r="I236"/>
@@ -6677,7 +6820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G237"/>
       <c r="H237"/>
       <c r="I237"/>
@@ -6691,7 +6834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="238" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G238"/>
       <c r="H238"/>
       <c r="I238"/>
@@ -6705,7 +6848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G239"/>
       <c r="H239"/>
       <c r="I239"/>
@@ -6719,7 +6862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G240"/>
       <c r="H240"/>
       <c r="I240"/>
@@ -6733,7 +6876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G241"/>
       <c r="H241"/>
       <c r="I241"/>
@@ -6747,7 +6890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G242"/>
       <c r="H242"/>
       <c r="I242"/>
@@ -6761,7 +6904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G243"/>
       <c r="H243"/>
       <c r="I243"/>
@@ -6775,7 +6918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G244"/>
       <c r="H244"/>
       <c r="I244"/>
@@ -6789,7 +6932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G245"/>
       <c r="H245"/>
       <c r="I245"/>
@@ -6803,7 +6946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G246"/>
       <c r="H246"/>
       <c r="I246"/>
@@ -6817,7 +6960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="247" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G247"/>
       <c r="H247"/>
       <c r="I247"/>
@@ -6831,7 +6974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G248"/>
       <c r="H248"/>
       <c r="I248"/>
@@ -6845,7 +6988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G249"/>
       <c r="H249"/>
       <c r="I249"/>
@@ -6859,7 +7002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G250"/>
       <c r="H250"/>
       <c r="I250"/>
@@ -6873,7 +7016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G251"/>
       <c r="H251"/>
       <c r="I251"/>
@@ -6887,7 +7030,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G252"/>
       <c r="H252"/>
       <c r="I252"/>
@@ -6901,7 +7044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G253"/>
       <c r="H253"/>
       <c r="I253"/>
@@ -6915,7 +7058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G254"/>
       <c r="H254"/>
       <c r="I254"/>
@@ -6929,7 +7072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G255"/>
       <c r="H255"/>
       <c r="I255"/>
@@ -6943,7 +7086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G256"/>
       <c r="H256"/>
       <c r="I256"/>
@@ -6957,7 +7100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G257"/>
       <c r="H257"/>
       <c r="I257"/>
@@ -6971,7 +7114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G258"/>
       <c r="H258"/>
       <c r="I258"/>
@@ -6985,7 +7128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G259"/>
       <c r="H259"/>
       <c r="I259"/>
@@ -6999,7 +7142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="260" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G260"/>
       <c r="H260"/>
       <c r="I260"/>
@@ -7013,7 +7156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G261"/>
       <c r="H261"/>
       <c r="I261"/>
@@ -7027,7 +7170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G262"/>
       <c r="H262"/>
       <c r="I262"/>
@@ -7041,7 +7184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G263"/>
       <c r="H263"/>
       <c r="I263"/>
@@ -7055,7 +7198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G264"/>
       <c r="H264"/>
       <c r="I264"/>
@@ -7069,7 +7212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G265"/>
       <c r="H265"/>
       <c r="I265"/>
@@ -7083,7 +7226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G266"/>
       <c r="H266"/>
       <c r="I266"/>
@@ -7097,7 +7240,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G267"/>
       <c r="H267"/>
       <c r="I267"/>
@@ -7111,7 +7254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="268" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G268"/>
       <c r="H268"/>
       <c r="I268"/>
@@ -7125,7 +7268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G269"/>
       <c r="H269"/>
       <c r="I269"/>
@@ -7139,7 +7282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G270"/>
       <c r="H270"/>
       <c r="I270"/>
@@ -7153,7 +7296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="271" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G271"/>
       <c r="H271"/>
       <c r="I271"/>
@@ -7167,7 +7310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G272"/>
       <c r="H272"/>
       <c r="I272"/>
@@ -7181,7 +7324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="273" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G273"/>
       <c r="H273"/>
       <c r="I273"/>
@@ -7195,7 +7338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G274"/>
       <c r="H274"/>
       <c r="I274"/>
@@ -7209,7 +7352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G275"/>
       <c r="H275"/>
       <c r="I275"/>
@@ -7223,7 +7366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G276"/>
       <c r="H276"/>
       <c r="I276"/>
@@ -7237,7 +7380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G277"/>
       <c r="H277"/>
       <c r="I277"/>
@@ -7251,7 +7394,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G278"/>
       <c r="H278"/>
       <c r="I278"/>
@@ -7265,7 +7408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G279"/>
       <c r="H279"/>
       <c r="I279"/>
@@ -7279,7 +7422,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="280" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G280"/>
       <c r="H280"/>
       <c r="I280"/>
@@ -7293,7 +7436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G281"/>
       <c r="H281"/>
       <c r="I281"/>
@@ -7307,7 +7450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G282"/>
       <c r="H282"/>
       <c r="I282"/>
@@ -7321,7 +7464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G283"/>
       <c r="H283"/>
       <c r="I283"/>
@@ -7335,7 +7478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="284" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G284"/>
       <c r="H284"/>
       <c r="I284"/>
@@ -7349,7 +7492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G285"/>
       <c r="H285"/>
       <c r="I285"/>
@@ -7363,7 +7506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G286"/>
       <c r="H286"/>
       <c r="I286"/>
@@ -7377,7 +7520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G287"/>
       <c r="H287"/>
       <c r="I287"/>
@@ -7391,7 +7534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G288"/>
       <c r="H288"/>
       <c r="I288"/>
@@ -7405,7 +7548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G289"/>
       <c r="H289"/>
       <c r="I289"/>
@@ -7419,7 +7562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G290"/>
       <c r="H290"/>
       <c r="I290"/>
@@ -7433,7 +7576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G291"/>
       <c r="H291"/>
       <c r="I291"/>
@@ -7447,7 +7590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G292"/>
       <c r="H292"/>
       <c r="I292"/>
@@ -7461,7 +7604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G293"/>
       <c r="H293"/>
       <c r="I293"/>
@@ -7475,7 +7618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G294"/>
       <c r="H294"/>
       <c r="I294"/>
@@ -7489,7 +7632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G295"/>
       <c r="H295"/>
       <c r="I295"/>
@@ -7503,7 +7646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="296" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G296"/>
       <c r="H296"/>
       <c r="I296"/>
@@ -7517,7 +7660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="297" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G297"/>
       <c r="H297"/>
       <c r="I297"/>
@@ -7531,7 +7674,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="298" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G298"/>
       <c r="H298"/>
       <c r="I298"/>
@@ -7545,7 +7688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="299" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G299"/>
       <c r="H299"/>
       <c r="I299"/>
@@ -7559,7 +7702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G300"/>
       <c r="H300"/>
       <c r="I300"/>
@@ -7573,7 +7716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="301" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G301"/>
       <c r="H301"/>
       <c r="I301"/>
@@ -7587,7 +7730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="302" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G302"/>
       <c r="H302"/>
       <c r="I302"/>
@@ -7601,7 +7744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G303"/>
       <c r="H303"/>
       <c r="I303"/>
@@ -7615,7 +7758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G304"/>
       <c r="H304"/>
       <c r="I304"/>
@@ -7629,7 +7772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G305"/>
       <c r="H305"/>
       <c r="I305"/>
@@ -7643,7 +7786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="306" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G306"/>
       <c r="H306"/>
       <c r="I306"/>
@@ -7657,7 +7800,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G307"/>
       <c r="H307"/>
       <c r="I307"/>
@@ -7671,7 +7814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="308" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G308"/>
       <c r="H308"/>
       <c r="I308"/>
@@ -7685,7 +7828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G309"/>
       <c r="H309"/>
       <c r="I309"/>
@@ -7699,7 +7842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G310"/>
       <c r="H310"/>
       <c r="I310"/>
@@ -7713,7 +7856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G311"/>
       <c r="H311"/>
       <c r="I311"/>
@@ -7727,7 +7870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G312"/>
       <c r="H312"/>
       <c r="I312"/>
@@ -7741,7 +7884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="313" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G313"/>
       <c r="H313"/>
       <c r="I313"/>
@@ -7755,7 +7898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="314" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G314"/>
       <c r="H314"/>
       <c r="I314"/>
@@ -7769,7 +7912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="315" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G315"/>
       <c r="H315"/>
       <c r="I315"/>
@@ -7783,7 +7926,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G316"/>
       <c r="H316"/>
       <c r="I316"/>
@@ -7797,7 +7940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G317"/>
       <c r="H317"/>
       <c r="I317"/>
@@ -7811,7 +7954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G318"/>
       <c r="H318"/>
       <c r="I318"/>
@@ -7825,7 +7968,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G319"/>
       <c r="H319"/>
       <c r="I319"/>
@@ -7839,7 +7982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G320"/>
       <c r="H320"/>
       <c r="I320"/>
@@ -7853,7 +7996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G321"/>
       <c r="H321"/>
       <c r="I321"/>
@@ -7867,7 +8010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G322"/>
       <c r="H322"/>
       <c r="I322"/>
@@ -7881,7 +8024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G323"/>
       <c r="H323"/>
       <c r="I323"/>
@@ -7895,7 +8038,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G324"/>
       <c r="H324"/>
       <c r="I324"/>
@@ -7909,7 +8052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G325"/>
       <c r="H325"/>
       <c r="I325"/>
@@ -7923,7 +8066,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G326"/>
       <c r="H326"/>
       <c r="I326"/>
@@ -7937,7 +8080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G327"/>
       <c r="H327"/>
       <c r="I327"/>
@@ -7951,7 +8094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G328"/>
       <c r="H328"/>
       <c r="I328"/>
@@ -7965,7 +8108,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G329"/>
       <c r="H329"/>
       <c r="I329"/>
@@ -7979,7 +8122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G330"/>
       <c r="H330"/>
       <c r="I330"/>
@@ -7993,7 +8136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G331"/>
       <c r="H331"/>
       <c r="I331"/>
@@ -8007,7 +8150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G332"/>
       <c r="H332"/>
       <c r="I332"/>
@@ -8021,7 +8164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G333"/>
       <c r="H333"/>
       <c r="I333"/>
@@ -8035,7 +8178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="334" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G334"/>
       <c r="H334"/>
       <c r="I334"/>
@@ -8049,7 +8192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="335" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G335"/>
       <c r="H335"/>
       <c r="I335"/>
@@ -8063,7 +8206,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G336"/>
       <c r="H336"/>
       <c r="I336"/>
@@ -8077,7 +8220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G337"/>
       <c r="H337"/>
       <c r="I337"/>
@@ -8091,7 +8234,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G338"/>
       <c r="H338"/>
       <c r="I338"/>
@@ -8105,7 +8248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G339"/>
       <c r="H339"/>
       <c r="I339"/>
@@ -8119,7 +8262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="340" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G340"/>
       <c r="H340"/>
       <c r="I340"/>
@@ -8133,7 +8276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G341"/>
       <c r="H341"/>
       <c r="I341"/>
@@ -8147,7 +8290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="342" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G342"/>
       <c r="H342"/>
       <c r="I342"/>
@@ -8161,7 +8304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G343"/>
       <c r="H343"/>
       <c r="I343"/>
@@ -8175,7 +8318,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="344" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G344"/>
       <c r="H344"/>
       <c r="I344"/>
@@ -8189,7 +8332,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G345"/>
       <c r="H345"/>
       <c r="I345"/>
@@ -8203,7 +8346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="346" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G346"/>
       <c r="H346"/>
       <c r="I346"/>
@@ -8217,7 +8360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="347" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G347"/>
       <c r="H347"/>
       <c r="I347"/>
@@ -8231,7 +8374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G348"/>
       <c r="H348"/>
       <c r="I348"/>
@@ -8245,7 +8388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G349"/>
       <c r="H349"/>
       <c r="I349"/>
@@ -8259,7 +8402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G350"/>
       <c r="H350"/>
       <c r="I350"/>
@@ -8273,7 +8416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G351"/>
       <c r="H351"/>
       <c r="I351"/>
@@ -8287,7 +8430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G352"/>
       <c r="H352"/>
       <c r="I352"/>
@@ -8301,7 +8444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G353"/>
       <c r="H353"/>
       <c r="I353"/>
@@ -8315,7 +8458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G354"/>
       <c r="H354"/>
       <c r="I354"/>
@@ -8329,7 +8472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G355"/>
       <c r="H355"/>
       <c r="I355"/>
@@ -8343,7 +8486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="356" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G356"/>
       <c r="H356"/>
       <c r="I356"/>
@@ -8357,7 +8500,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="357" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G357"/>
       <c r="H357"/>
       <c r="I357"/>
@@ -8371,7 +8514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="358" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G358"/>
       <c r="H358"/>
       <c r="I358"/>
@@ -8385,7 +8528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G359"/>
       <c r="H359"/>
       <c r="I359"/>
@@ -8399,7 +8542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="360" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G360"/>
       <c r="H360"/>
       <c r="I360"/>
@@ -8413,7 +8556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="361" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G361"/>
       <c r="H361"/>
       <c r="I361"/>
@@ -8427,7 +8570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="362" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G362"/>
       <c r="H362"/>
       <c r="I362"/>
@@ -8441,7 +8584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="363" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G363"/>
       <c r="H363"/>
       <c r="I363"/>
@@ -8455,7 +8598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="364" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G364"/>
       <c r="H364"/>
       <c r="I364"/>
@@ -8469,7 +8612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="365" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G365"/>
       <c r="H365"/>
       <c r="I365"/>
@@ -8483,7 +8626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G366"/>
       <c r="H366"/>
       <c r="I366"/>
@@ -8497,7 +8640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="367" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G367"/>
       <c r="H367"/>
       <c r="I367"/>
@@ -8511,7 +8654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="368" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G368"/>
       <c r="H368"/>
       <c r="I368"/>
@@ -8525,7 +8668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="369" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G369"/>
       <c r="H369"/>
       <c r="I369"/>
@@ -8539,7 +8682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="370" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G370"/>
       <c r="H370"/>
       <c r="I370"/>
@@ -8553,7 +8696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="371" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G371"/>
       <c r="H371"/>
       <c r="I371"/>
@@ -8567,7 +8710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="372" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G372"/>
       <c r="H372"/>
       <c r="I372"/>
@@ -8581,7 +8724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="373" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G373"/>
       <c r="H373"/>
       <c r="I373"/>
@@ -8595,7 +8738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G374"/>
       <c r="H374"/>
       <c r="I374"/>
@@ -8609,7 +8752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="375" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G375"/>
       <c r="H375"/>
       <c r="I375"/>
@@ -8623,7 +8766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="376" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G376"/>
       <c r="H376"/>
       <c r="I376"/>
@@ -8637,7 +8780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G377"/>
       <c r="H377"/>
       <c r="I377"/>
@@ -8651,7 +8794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G378"/>
       <c r="H378"/>
       <c r="I378"/>
@@ -8665,7 +8808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="379" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G379"/>
       <c r="H379"/>
       <c r="I379"/>
@@ -8679,7 +8822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G380"/>
       <c r="H380"/>
       <c r="I380"/>
@@ -8693,7 +8836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="381" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G381"/>
       <c r="H381"/>
       <c r="I381"/>
@@ -8707,7 +8850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G382"/>
       <c r="H382"/>
       <c r="I382"/>
@@ -8721,7 +8864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="383" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G383"/>
       <c r="H383"/>
       <c r="I383"/>
@@ -8735,7 +8878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="384" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G384"/>
       <c r="H384"/>
       <c r="I384"/>
@@ -8749,7 +8892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="385" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="385" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G385"/>
       <c r="H385"/>
       <c r="I385"/>
@@ -8763,7 +8906,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="386" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="386" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G386"/>
       <c r="H386"/>
       <c r="I386"/>
@@ -8777,21 +8920,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="387" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G387"/>
       <c r="H387"/>
       <c r="I387"/>
       <c r="U387" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V387" s="4" t="s">
+      <c r="V387" s="9" t="s">
         <v>448</v>
       </c>
       <c r="Z387" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="388" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G388"/>
       <c r="H388"/>
       <c r="I388"/>
@@ -8805,7 +8948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="389" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="389" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G389"/>
       <c r="H389"/>
       <c r="I389"/>
@@ -8819,7 +8962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="390" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="390" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G390"/>
       <c r="H390"/>
       <c r="I390"/>
@@ -8833,17 +8976,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="7:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="391" spans="7:26" ht="16" x14ac:dyDescent="0.2">
       <c r="G391"/>
       <c r="H391"/>
       <c r="I391"/>
       <c r="U391" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V391" s="4" t="s">
+      <c r="V391" s="9" t="s">
         <v>457</v>
       </c>
       <c r="Z391" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="392" spans="7:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="U392" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="V392" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="Z392" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="393" spans="7:26" ht="14" x14ac:dyDescent="0.2">
+      <c r="U393" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="V393" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="Z393" s="10" t="s">
         <v>7</v>
       </c>
     </row>

--- a/docs/s2t_task/s2t_files_examples/json_S2T_пример JSON.xlsx
+++ b/docs/s2t_task/s2t_files_examples/json_S2T_пример JSON.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/synikolaev/data_lineage_monorepo/docs/s2t_task/s2t_files_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FEA9C0-D6FB-494F-A765-3FE33E41EDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9BCB97-3319-CA40-A548-745DC25B4068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -462,7 +462,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="497">
   <si>
     <t>Source/Target</t>
   </si>
@@ -2529,6 +2529,12 @@
   </si>
   <si>
     <t>JSON_MODEL69666-V2</t>
+  </si>
+  <si>
+    <t>JSON_MODEL69666-V3</t>
+  </si>
+  <si>
+    <t>loanApplication.creditParameters.leasingDevilCars3</t>
   </si>
 </sst>
 </file>
@@ -3349,7 +3355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF393"/>
+  <dimension ref="A1:AF394"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -9012,6 +9018,17 @@
         <v>7</v>
       </c>
     </row>
+    <row r="394" spans="7:26" ht="14" x14ac:dyDescent="0.2">
+      <c r="U394" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="V394" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="Z394" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:AF12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">

--- a/docs/s2t_task/s2t_files_examples/json_S2T_пример JSON.xlsx
+++ b/docs/s2t_task/s2t_files_examples/json_S2T_пример JSON.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/synikolaev/data_lineage_monorepo/docs/s2t_task/s2t_files_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9BCB97-3319-CA40-A548-745DC25B4068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6AEB0B-CBC6-F74C-A73F-5CFA9C50EC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2528,13 +2528,13 @@
     <t>loanApplication.creditParameters.leasingDevilCars2</t>
   </si>
   <si>
-    <t>JSON_MODEL69666-V2</t>
-  </si>
-  <si>
-    <t>JSON_MODEL69666-V3</t>
-  </si>
-  <si>
     <t>loanApplication.creditParameters.leasingDevilCars3</t>
+  </si>
+  <si>
+    <t>JSON_MODEL69666777-V3</t>
+  </si>
+  <si>
+    <t>JSON_MODEL69666777-V2</t>
   </si>
 </sst>
 </file>
@@ -9007,9 +9007,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="393" spans="7:26" ht="14" x14ac:dyDescent="0.2">
+    <row r="393" spans="7:26" ht="28" x14ac:dyDescent="0.2">
       <c r="U393" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="V393" s="1" t="s">
         <v>493</v>
@@ -9018,12 +9018,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="7:26" ht="14" x14ac:dyDescent="0.2">
+    <row r="394" spans="7:26" ht="28" x14ac:dyDescent="0.2">
       <c r="U394" s="1" t="s">
         <v>495</v>
       </c>
       <c r="V394" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Z394" s="10" t="s">
         <v>7</v>
